--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -4328,10 +4328,10 @@
         <v>悪徳商法・詐欺被害・契約トラブルなどの消費生活相談窓口。無料。</v>
       </c>
       <c r="H84" t="str">
-        <v xml:space="preserve">【消費生活・詐欺被害の困りごとがある】 </v>
+        <v>【消費生活・詐欺被害の困りごとがある】 または 【本人が60歳以上】</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>日本語欄に「本人が60歳以上」の記載が抜けていたため追加（condは元々age&gt;=60を含んでいた。コード変更なし）</v>
       </c>
       <c r="J84" t="str">
         <v>https://www.city.nagoya.jp/kurashi/shouhi/1016390/1016404.html</v>

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -4093,10 +4093,10 @@
         <v>心理的な理由で登校できない小中学生と保護者の教育相談機関。学校を通じて申込。</v>
       </c>
       <c r="H79" t="str">
-        <v>【不登校の子どもがいる】 または 【子どもの教育・学校の困りごとがある】 または 【ひきこもり・不登校の困りごとがある】</v>
+        <v>【子どもが15歳以下（小中学生相当）】で、【不登校・登校しぶり】または【子どもの教育・学校の困りごとがある】または【ひきこもり・不登校の困りごとがある】</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>対象は小中学生限定だが、condに年齢条件がなく高校生や子ども未登録でもマッチしていたため、子どもの年齢15歳以下の条件を追加</v>
       </c>
       <c r="J79" t="str">
         <v>https://www.city.nagoya.jp/kodomo/schools/1015850/1017055.html</v>
@@ -4114,7 +4114,7 @@
         <v>電話相談 ハートフレンドなごや: https://nagoya.fureai-cloud.jp/_view/sodan/home/index</v>
       </c>
       <c r="O79" t="str">
-        <v>s.children?.some(c =&gt; c.status === 'futoko') || s.concerns?.includes('education') || s.concerns?.includes('hikikomori_concern')</v>
+        <v>s.children?.some(c =&gt; (c.age || c) &lt;= 15 &amp;&amp; (c.status === 'futoko' || s.concerns?.includes('education') || s.concerns?.includes('hikikomori_concern')))</v>
       </c>
     </row>
     <row r="80">

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -1222,10 +1222,10 @@
         <v>65歳以上を対象にインフルエンザ予防接種費用の一部を助成（自己負担約1,500円）。</v>
       </c>
       <c r="H18" t="str">
-        <v>【本人が65歳以上】 または 【高齢者と同居している】</v>
+        <v>【本人が65歳以上】</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>「高齢者と同居している」の条件をユーザー指示により削除（本人の年齢のみを対象とする）</v>
       </c>
       <c r="J18" t="str">
         <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
@@ -1243,7 +1243,7 @@
         <v>各保健センター一覧: https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="O18" t="str">
-        <v>parseInt(s.age) &gt;= 65 || s.elderlyMembers?.length &gt; 0</v>
+        <v>parseInt(s.age) &gt;= 65</v>
       </c>
     </row>
     <row r="19">

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -1222,10 +1222,10 @@
         <v>65歳以上を対象にインフルエンザ予防接種費用の一部を助成（自己負担約1,500円）。</v>
       </c>
       <c r="H18" t="str">
-        <v>【本人が65歳以上】</v>
+        <v>【本人が65歳以上】 または 【高齢者と同居している】</v>
       </c>
       <c r="I18" t="str">
-        <v>「高齢者と同居している」の条件をユーザー指示により削除（本人の年齢のみを対象とする）</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009500/1009599/1009600.html</v>
@@ -1243,7 +1243,7 @@
         <v>各保健センター一覧: https://www.kaigo-wel.city.nagoya.jp/view/kaigo/yobou/toiawase/ichiran.html</v>
       </c>
       <c r="O18" t="str">
-        <v>parseInt(s.age) &gt;= 65</v>
+        <v>parseInt(s.age) &gt;= 65 || s.elderlyMembers?.length &gt; 0</v>
       </c>
     </row>
     <row r="19">

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -1207,7 +1207,7 @@
         <v>高齢者インフルエンザ予防接種費用助成</v>
       </c>
       <c r="C18" t="str">
-        <v>医療・健康</v>
+        <v>高齢者</v>
       </c>
       <c r="D18" t="str">
         <v>本人・大人</v>

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -1834,10 +1834,10 @@
         <v>身体・知的・精神障害者のみの世帯等に、1日1食・週7回を限度に配食し、あわせて安否確認を行います。</v>
       </c>
       <c r="H31" t="str">
-        <v>【身体障害等のある方がいる】 または 【知的障害のある方がいる】 または 【精神障害のある方がいる】</v>
+        <v>【一人暮らし】 かつ （【身体障害等のある方がいる】 または 【知的障害のある方がいる】 または 【精神障害のある方がいる】）</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>制度対象が「障害者のみの世帯」だがcondが世帯構成を見ておらず同居家族に障害者がいる全員にマッチしていたため、一人暮らし条件(living===alone)を追加</v>
       </c>
       <c r="J31" t="str">
         <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
@@ -1855,7 +1855,7 @@
         <v>障害者基幹相談支援センター一覧: https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="O31" t="str">
-        <v>s.disabledMembers?.includes('disabled') || s.disabledMembers?.includes('intellectual') || s.disabledMembers?.includes('mental')</v>
+        <v>s.living === 'alone' &amp;&amp; (s.disabledMembers?.includes('disabled') || s.disabledMembers?.includes('intellectual') || s.disabledMembers?.includes('mental'))</v>
       </c>
     </row>
     <row r="32">

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -1834,10 +1834,10 @@
         <v>身体・知的・精神障害者のみの世帯等に、1日1食・週7回を限度に配食し、あわせて安否確認を行います。</v>
       </c>
       <c r="H31" t="str">
-        <v>【一人暮らし】 かつ （【身体障害等のある方がいる】 または 【知的障害のある方がいる】 または 【精神障害のある方がいる】）</v>
+        <v>（【一人暮らし】 または 【同居家族の詳細が未入力】） かつ （【身体障害等のある方がいる】 または 【知的障害のある方がいる】 または 【精神障害のある方がいる】）</v>
       </c>
       <c r="I31" t="str">
-        <v>制度対象が「障害者のみの世帯」だがcondが世帯構成を見ておらず同居家族に障害者がいる全員にマッチしていたため、一人暮らし条件(living===alone)を追加</v>
+        <v>制度対象が「障害者のみの世帯」だがcondが世帯構成を見ておらず同居家族に障害者がいる全員にマッチしていたため、一人暮らし条件(living===alone)を追加。ただし「一人暮らし」未選択・「家族と同居」選択でも同居家族（成人家族・高齢家族）の詳細を1件も入力していない場合は一人暮らし相当とみなしてマッチするよう緩和</v>
       </c>
       <c r="J31" t="str">
         <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
@@ -1855,7 +1855,7 @@
         <v>障害者基幹相談支援センター一覧: https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="O31" t="str">
-        <v>s.living === 'alone' &amp;&amp; (s.disabledMembers?.includes('disabled') || s.disabledMembers?.includes('intellectual') || s.disabledMembers?.includes('mental'))</v>
+        <v>(s.living === 'alone' || (!(s.adultMembers?.length &gt; 0) &amp;&amp; !(s.elderlyMembers?.length &gt; 0))) &amp;&amp; (s.disabledMembers?.includes('disabled') || s.disabledMembers?.includes('intellectual') || s.disabledMembers?.includes('mental'))</v>
       </c>
     </row>
     <row r="32">

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -1834,10 +1834,10 @@
         <v>身体・知的・精神障害者のみの世帯等に、1日1食・週7回を限度に配食し、あわせて安否確認を行います。</v>
       </c>
       <c r="H31" t="str">
-        <v>（【一人暮らし】 または 【同居家族の詳細が未入力】） かつ （【身体障害等のある方がいる】 または 【知的障害のある方がいる】 または 【精神障害のある方がいる】）</v>
+        <v>【一人暮らし】 かつ （【身体障害等のある方がいる】 または 【知的障害のある方がいる】 または 【精神障害のある方がいる】）</v>
       </c>
       <c r="I31" t="str">
-        <v>制度対象が「障害者のみの世帯」だがcondが世帯構成を見ておらず同居家族に障害者がいる全員にマッチしていたため、一人暮らし条件(living===alone)を追加。ただし「一人暮らし」未選択・「家族と同居」選択でも同居家族（成人家族・高齢家族）の詳細を1件も入力していない場合は一人暮らし相当とみなしてマッチするよう緩和</v>
+        <v>制度対象が「障害者のみの世帯」だがcondが世帯構成を見ておらず同居家族に障害者がいる全員にマッチしていたため、一人暮らし条件(living===alone)を追加</v>
       </c>
       <c r="J31" t="str">
         <v>https://www.kaigo-wel.city.nagoya.jp/view/wel/service/othersystems/haishoku.html</v>
@@ -1855,7 +1855,7 @@
         <v>障害者基幹相談支援センター一覧: https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016662/1016664.html</v>
       </c>
       <c r="O31" t="str">
-        <v>(s.living === 'alone' || (!(s.adultMembers?.length &gt; 0) &amp;&amp; !(s.elderlyMembers?.length &gt; 0))) &amp;&amp; (s.disabledMembers?.includes('disabled') || s.disabledMembers?.includes('intellectual') || s.disabledMembers?.includes('mental'))</v>
+        <v>s.living === 'alone' &amp;&amp; (s.disabledMembers?.includes('disabled') || s.disabledMembers?.includes('intellectual') || s.disabledMembers?.includes('mental'))</v>
       </c>
     </row>
     <row r="32">

--- a/確認中services-match-conditions-v2 .xlsx
+++ b/確認中services-match-conditions-v2 .xlsx
@@ -1740,10 +1740,10 @@
       </c>
       <c r="H29" t="str" xml:space="preserve">
         <v xml:space="preserve">【障害等のある方】で「精神障害（手帳あり）」_x000d_
-または「発達障害の疑い（診断なし）」または 【障害福祉サービスの困りごとがある】または「グレーゾーンの方がいる」</v>
+または「未診断で障害の疑いあり」または 【障害福祉サービスの困りごとがある】または「グレーゾーンの方がいる」</v>
       </c>
       <c r="I29" t="str">
-        <v>申請・問合せ先に対応曜日と時間を追加。マッチ条件の【身体障害等のある方がいる】を精神障害者に変更</v>
+        <v>プロフィールのボタン表記変更「発達障害の疑い（診断なし）」→「未診断で障害の疑いあり」に伴い和訳を更新</v>
       </c>
       <c r="J29" t="str">
         <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016579/1016622/index.html</v>
@@ -1787,10 +1787,10 @@
         <v>一般企業への就職を目指す障害・発達困難のある方への訓練・支援。手帳なしでも利用できる場合あり。</v>
       </c>
       <c r="H30" t="str">
-        <v>【障害等のある方】で「身体障害（手帳あり）」「知的障害（療育手帳）」「精神障害（手帳あり）」「発達障害の疑い（診断なし）」または 【障害福祉サービスの困りごとがある】または「グレーゾーンの方がいる」</v>
+        <v>【障害等のある方】で「身体障害（手帳あり）」「知的障害（療育手帳）」「精神障害（手帳あり）」「未診断で障害の疑いあり」または 【障害福祉サービスの困りごとがある】または「グレーゾーンの方がいる」</v>
       </c>
       <c r="I30" t="str">
-        <v>申請・問合せ先の各区役所 福祉課を健康福祉局 障害福祉部 障害者支援課 就労支援の推進担当に変更。マッチ条件を障害全般に変更</v>
+        <v>プロフィールのボタン表記変更「発達障害の疑い（診断なし）」→「未診断で障害の疑いあり」に伴い和訳を更新</v>
       </c>
       <c r="J30" t="str">
         <v>https://www.city.nagoya.jp/kenkofukushi/shougaisha/1016674/1016675.html</v>
@@ -1881,10 +1881,10 @@
         <v>こころの不調・発達の困難を感じたら、電話またはLINE相談（LINEチャット相談）で無料相談できます。</v>
       </c>
       <c r="H32" t="str">
-        <v>「精神障害（手帳あり）」または 「発達障害の疑い（診断なし）」または 【心の健康・メンタルの困りごとがある】または「グレーゾーンの方がいる」</v>
+        <v>「精神障害（手帳あり）」または 「未診断で障害の疑いあり」または 【心の健康・メンタルの困りごとがある】または「グレーゾーンの方がいる」</v>
       </c>
       <c r="I32" t="str">
-        <v>LINE相談（LINEチャット相談）ありを追加。マッチ条件の【身体障害等のある方がいる】を精神障害者に変更</v>
+        <v>プロフィールのボタン表記変更「発達障害の疑い（診断なし）」→「未診断で障害の疑いあり」に伴い和訳を更新</v>
       </c>
       <c r="J32" t="str">
         <v>https://www.city.nagoya.jp/kenkofukushi/kenkoinfo/1009444/1009454.html</v>
